--- a/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA CIM AHO QC COPART SR.xlsx
+++ b/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA CIM AHO QC COPART SR.xlsx
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Itaperucu</t>
+          <t>Itaperuçu</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -11974,7 +11974,7 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -13486,7 +13486,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sao Jose dos Pinhais</t>
+          <t>São José dos Pinhais</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -13496,7 +13496,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Araucaria</t>
+          <t>Araucária</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -13546,7 +13546,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Itaperucu</t>
+          <t>Itaperuçu</t>
         </is>
       </c>
       <c r="B24" t="n">

--- a/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA CIM AHO QC COPART SR.xlsx
+++ b/01 - REDE CREDENCIADA/Paraná Clínicas/REDE PARANA CIM AHO QC COPART SR.xlsx
@@ -49,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6B4E"/>
+        <fgColor rgb="008E0E28"/>
       </patternFill>
     </fill>
   </fills>
